--- a/Medição - Contratada/IRON/Contrato nº 4600686987_Fat._Lote1 - RJ.xlsx
+++ b/Medição - Contratada/IRON/Contrato nº 4600686987_Fat._Lote1 - RJ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thelmo\nitro\Medição - Contratada\IRON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PainelNovo\Medição - Contratada\IRON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423181AF-7085-46B7-8465-5E65B092ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2023D9-AB32-48FD-90CC-9B2205C88BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId23" roundtripDataChecksum="34oD2PTMo2tTZPMOHyLqYVrzjSBzwU5tr1oSokZuaJ0="/>
@@ -1552,7 +1555,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.000;[Red]#,##0.000"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1671,13 +1674,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1720,11 +1716,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1E4E79"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1789,7 +1787,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -2239,17 +2237,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2262,22 +2249,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2490,26 +2466,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2563,105 +2539,151 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="21" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="21" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="18" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="9" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="9" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2677,84 +2699,29 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="50">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2765,12 +2732,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -2779,7 +2740,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2792,13 +2753,184 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
@@ -3260,10 +3392,21 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
           <color indexed="64"/>
-        </bottom>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3277,6 +3420,20 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3299,218 +3456,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="9"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3643,65 +3588,65 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ConsolidadoRJ" displayName="ConsolidadoRJ" ref="A3:S30" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20">
-  <autoFilter ref="A3:S30" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ConsolidadoRJ" displayName="ConsolidadoRJ" ref="A3:S12" headerRowDxfId="37" dataDxfId="35" totalsRowDxfId="33" headerRowBorderDxfId="36" tableBorderDxfId="34">
+  <autoFilter ref="A3:S12" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="MEDIDAS CONTRATO" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Padrão" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ø" dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="MEDIDAS CONTRATO" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Padrão" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ø" dataDxfId="30">
       <calculatedColumnFormula>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="A" dataDxfId="15">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="A" dataDxfId="29">
       <calculatedColumnFormula>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="L" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="L" dataDxfId="28">
       <calculatedColumnFormula>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="P" dataDxfId="13">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="P" dataDxfId="27">
       <calculatedColumnFormula>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="cm³ = V1" dataDxfId="12">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="cm³ = V1" dataDxfId="26">
       <calculatedColumnFormula>IFERROR( Consolidado!$D4*Consolidado!$E4*Consolidado!$F4, "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="cm³ = V2" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="cm³ = V2" dataDxfId="25">
       <calculatedColumnFormula>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="FC = V1/V2" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="QUAm-1" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="QBm" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QDm" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="QNm" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="QUAm" dataDxfId="5">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="FC = V1/V2" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="QUAm-1" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="QBm" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QDm" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="QNm" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="QUAm" dataDxfId="19">
       <calculatedColumnFormula>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="UA" dataDxfId="4">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="UA" dataDxfId="18">
       <calculatedColumnFormula>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="$ Unitário" dataDxfId="3">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="$ Unitário" dataDxfId="17">
       <calculatedColumnFormula>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="$ Total" dataDxfId="2">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="$ Total" dataDxfId="16">
       <calculatedColumnFormula>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Tabela" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Contrato" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Tabela" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Contrato" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}" name="Padrão" displayName="Padrão" ref="A1:A54" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}" name="Padrão" displayName="Padrão" ref="A1:A54" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A1:A54" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FC834546-F8C2-43F1-8653-2C9C306C6853}" name="Padrão" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{FC834546-F8C2-43F1-8653-2C9C306C6853}" name="Padrão" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}" name="LinhaPPU" displayName="LinhaPPU" ref="E1:E29" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}" name="LinhaPPU" displayName="LinhaPPU" ref="E1:E29" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="E1:E29" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A3A4CE9E-7B99-4F3C-B222-4D496C2EDC0C}" name="Linha de serviço PPU"/>
@@ -3718,7 +3663,7 @@
     <tableColumn id="3" xr3:uid="{F8835F93-6997-4EE6-A8A2-5BBA9F5F9A23}" name="DESCRIÇÃO"/>
     <tableColumn id="2" xr3:uid="{D294162E-0115-4594-923D-631C31B74466}" name="Linha de Serviço PPU"/>
     <tableColumn id="4" xr3:uid="{A9203A65-B976-413C-97EB-229EAEF64D66}" name="UNID."/>
-    <tableColumn id="6" xr3:uid="{BBC3EA5F-CFDD-489F-BD88-580B0C945906}" name="PREÇO UNITÁRIO " dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{BBC3EA5F-CFDD-489F-BD88-580B0C945906}" name="PREÇO UNITÁRIO " dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{8FC6BA38-CE26-4D70-9856-F81EFB0A1FF9}" name="Descrição da Linha de Serviço"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3736,17 +3681,17 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}" name="MedidasContrato" displayName="MedidasContrato" ref="N1:R124" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}" name="MedidasContrato" displayName="MedidasContrato" ref="N1:R124" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="N1:R124" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:R124">
     <sortCondition ref="N1:N124"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{848A6E3D-D10C-4C28-A755-1DAD0EF94CF9}" name="MEDIDAS CONTRATO" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{287CB8E4-DBEC-4AE7-A40F-F2A76BFF2D87}" name="Ø" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{38CAEDAB-4961-4068-8C60-2826957DFF9B}" name="A" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{8EAB565D-87A9-4B0E-BCC0-704CC37666E9}" name="L" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{33CC69D2-CED7-4EB1-AF77-D6211E14BE46}" name="P" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{848A6E3D-D10C-4C28-A755-1DAD0EF94CF9}" name="MEDIDAS CONTRATO" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{287CB8E4-DBEC-4AE7-A40F-F2A76BFF2D87}" name="Ø" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{38CAEDAB-4961-4068-8C60-2826957DFF9B}" name="A" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{8EAB565D-87A9-4B0E-BCC0-704CC37666E9}" name="L" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{33CC69D2-CED7-4EB1-AF77-D6211E14BE46}" name="P" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3989,49 +3934,49 @@
     </row>
     <row r="2" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="144"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="162"/>
       <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="144"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="162"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="147"/>
+      <c r="C4" s="165"/>
       <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
@@ -4046,7 +3991,7 @@
         <v>5</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="148" t="s">
+      <c r="L4" s="166" t="s">
         <v>6</v>
       </c>
       <c r="M4" s="8" t="s">
@@ -4060,10 +4005,10 @@
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="150" t="s">
+      <c r="B5" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="149"/>
+      <c r="C5" s="154"/>
       <c r="D5" s="11">
         <v>4600686987</v>
       </c>
@@ -4078,7 +4023,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="13"/>
-      <c r="L5" s="149"/>
+      <c r="L5" s="154"/>
       <c r="M5" s="14" t="s">
         <v>11</v>
       </c>
@@ -4090,17 +4035,17 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="150" t="s">
+      <c r="B6" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="149"/>
+      <c r="C6" s="154"/>
       <c r="D6" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="154"/>
       <c r="I6" s="12" t="s">
         <v>14</v>
       </c>
@@ -4122,21 +4067,21 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="151"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
       <c r="I7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="173" t="s">
+      <c r="J7" s="132" t="s">
         <v>386</v>
       </c>
       <c r="K7" s="19"/>
-      <c r="L7" s="152"/>
+      <c r="L7" s="156"/>
       <c r="M7" s="20" t="s">
         <v>11</v>
       </c>
@@ -4178,13 +4123,13 @@
       <c r="C10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="153" t="s">
+      <c r="D10" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="155"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="136"/>
       <c r="I10" s="26" t="s">
         <v>20</v>
       </c>
@@ -4255,18 +4200,18 @@
       <c r="D12" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="156" t="s">
+      <c r="E12" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="157"/>
-      <c r="G12" s="157"/>
-      <c r="H12" s="157"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
       <c r="I12" s="91"/>
       <c r="J12" s="34"/>
       <c r="K12" s="35"/>
       <c r="L12" s="36"/>
       <c r="M12" s="37"/>
-      <c r="N12" s="139"/>
+      <c r="N12" s="150"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4295,11 +4240,11 @@
       </c>
       <c r="J13" s="40">
         <f>SUMIF(Consolidado!S:S,D12,Consolidado!O:O)</f>
-        <v>183422.07</v>
+        <v>207623.99</v>
       </c>
       <c r="K13" s="41">
         <f>J13*N5</f>
-        <v>179753.6286</v>
+        <v>203471.51019999999</v>
       </c>
       <c r="L13" s="42">
         <f>IFERROR(VLOOKUP(ARMCXDOC,TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,FALSE),"N/A")</f>
@@ -4307,9 +4252,9 @@
       </c>
       <c r="M13" s="43">
         <f>J13*L13</f>
-        <v>110053.242</v>
-      </c>
-      <c r="N13" s="140"/>
+        <v>124574.39399999999</v>
+      </c>
+      <c r="N13" s="151"/>
       <c r="P13" s="44"/>
       <c r="Q13" s="4"/>
     </row>
@@ -4319,11 +4264,11 @@
       <c r="C14" s="45"/>
       <c r="D14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QUAm-1])</f>
-        <v>142523</v>
+        <v>184924</v>
       </c>
       <c r="E14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QBm])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QDm])</f>
@@ -4331,18 +4276,18 @@
       </c>
       <c r="G14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QNm] )</f>
-        <v>41401</v>
+        <v>26066</v>
       </c>
       <c r="H14" s="99">
         <f>(D14-E14-F14)+G14</f>
-        <v>183924</v>
+        <v>210989</v>
       </c>
       <c r="I14" s="46"/>
       <c r="J14" s="47"/>
       <c r="K14" s="48"/>
       <c r="L14" s="49"/>
       <c r="M14" s="50"/>
-      <c r="N14" s="141"/>
+      <c r="N14" s="152"/>
       <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4352,18 +4297,18 @@
       <c r="D15" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="156" t="s">
+      <c r="E15" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="157"/>
-      <c r="G15" s="157"/>
-      <c r="H15" s="157"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="140"/>
       <c r="I15" s="97"/>
       <c r="J15" s="51"/>
       <c r="K15" s="35"/>
       <c r="L15" s="52"/>
       <c r="M15" s="53"/>
-      <c r="N15" s="139"/>
+      <c r="N15" s="150"/>
       <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4392,11 +4337,11 @@
       </c>
       <c r="J16" s="40">
         <f>SUMIF(Consolidado!S:S,D15,Consolidado!O:O)</f>
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="K16" s="41">
         <f>J16*N5</f>
-        <v>107.8</v>
+        <v>972.16</v>
       </c>
       <c r="L16" s="42">
         <f>IFERROR(VLOOKUP(ARMCXMID,TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,FALSE),"N/A")</f>
@@ -4404,9 +4349,9 @@
       </c>
       <c r="M16" s="43">
         <f>J16*L16</f>
-        <v>390.5</v>
-      </c>
-      <c r="N16" s="140"/>
+        <v>3521.6</v>
+      </c>
+      <c r="N16" s="151"/>
       <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4415,7 +4360,7 @@
       <c r="C17" s="45"/>
       <c r="D17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QUAm-1])</f>
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="E17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QBm])</f>
@@ -4427,18 +4372,18 @@
       </c>
       <c r="G17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QNm] )</f>
-        <v>101</v>
+        <v>882</v>
       </c>
       <c r="H17" s="99">
         <f>(D17-E17-F17)+G17</f>
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="I17" s="46"/>
       <c r="J17" s="47"/>
       <c r="K17" s="48"/>
       <c r="L17" s="49"/>
       <c r="M17" s="50"/>
-      <c r="N17" s="141"/>
+      <c r="N17" s="152"/>
       <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4448,17 +4393,17 @@
       <c r="D18" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="156" t="s">
+      <c r="E18" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="157"/>
-      <c r="G18" s="157"/>
-      <c r="H18" s="157"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="140"/>
       <c r="I18" s="97"/>
       <c r="J18" s="51"/>
       <c r="K18" s="35"/>
       <c r="M18" s="53"/>
-      <c r="N18" s="139"/>
+      <c r="N18" s="150"/>
       <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4501,7 +4446,7 @@
         <f>J19*L19</f>
         <v>8447.2849999999999</v>
       </c>
-      <c r="N19" s="140"/>
+      <c r="N19" s="151"/>
       <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4533,7 +4478,7 @@
       <c r="K20" s="48"/>
       <c r="L20" s="49"/>
       <c r="M20" s="50"/>
-      <c r="N20" s="141"/>
+      <c r="N20" s="152"/>
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4543,18 +4488,18 @@
       <c r="D21" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="156" t="s">
+      <c r="E21" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
-      <c r="H21" s="157"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
       <c r="I21" s="97"/>
       <c r="J21" s="51"/>
       <c r="K21" s="35"/>
       <c r="L21" s="52"/>
       <c r="M21" s="53"/>
-      <c r="N21" s="139"/>
+      <c r="N21" s="150"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4597,7 +4542,7 @@
         <f>J22*L22</f>
         <v>953.87</v>
       </c>
-      <c r="N22" s="140"/>
+      <c r="N22" s="151"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4629,7 +4574,7 @@
       <c r="K23" s="48"/>
       <c r="L23" s="49"/>
       <c r="M23" s="50"/>
-      <c r="N23" s="141"/>
+      <c r="N23" s="152"/>
       <c r="Q23" s="4"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4639,18 +4584,18 @@
       <c r="D24" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="156" t="s">
+      <c r="E24" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="157"/>
-      <c r="G24" s="157"/>
-      <c r="H24" s="157"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
       <c r="I24" s="97"/>
       <c r="J24" s="51"/>
       <c r="K24" s="35"/>
       <c r="L24" s="52"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="139"/>
+      <c r="N24" s="150"/>
       <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4693,7 +4638,7 @@
         <f>J25*L25</f>
         <v>0</v>
       </c>
-      <c r="N25" s="140"/>
+      <c r="N25" s="151"/>
       <c r="Q25" s="4"/>
     </row>
     <row r="26" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4725,7 +4670,7 @@
       <c r="K26" s="48"/>
       <c r="L26" s="49"/>
       <c r="M26" s="50"/>
-      <c r="N26" s="141"/>
+      <c r="N26" s="152"/>
       <c r="Q26" s="4"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4735,18 +4680,18 @@
       <c r="D27" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="156" t="s">
+      <c r="E27" s="157" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="157"/>
-      <c r="G27" s="157"/>
-      <c r="H27" s="157"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
       <c r="I27" s="102"/>
       <c r="J27" s="54"/>
       <c r="K27" s="41"/>
       <c r="L27" s="42"/>
       <c r="M27" s="43"/>
-      <c r="N27" s="139"/>
+      <c r="N27" s="150"/>
       <c r="Q27" s="4"/>
     </row>
     <row r="28" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4789,7 +4734,7 @@
         <f>J28*L28</f>
         <v>415.44</v>
       </c>
-      <c r="N28" s="140"/>
+      <c r="N28" s="151"/>
       <c r="Q28" s="4"/>
     </row>
     <row r="29" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4821,7 +4766,7 @@
       <c r="K29" s="48"/>
       <c r="L29" s="49"/>
       <c r="M29" s="50"/>
-      <c r="N29" s="141"/>
+      <c r="N29" s="152"/>
       <c r="Q29" s="4"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4830,16 +4775,16 @@
       <c r="C30" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="137" t="s">
+      <c r="D30" s="129" t="s">
         <v>137</v>
       </c>
-      <c r="E30" s="157" t="s">
+      <c r="E30" s="140" t="s">
         <v>344</v>
       </c>
-      <c r="F30" s="157"/>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="174" t="s">
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="140"/>
+      <c r="I30" s="133" t="s">
         <v>52</v>
       </c>
       <c r="J30" s="48">
@@ -4868,12 +4813,12 @@
       <c r="D31" s="96" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="157" t="s">
+      <c r="E31" s="140" t="s">
         <v>345</v>
       </c>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="140"/>
       <c r="I31" s="104" t="s">
         <v>52</v>
       </c>
@@ -4903,12 +4848,12 @@
       <c r="D32" s="96" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="157" t="s">
+      <c r="E32" s="140" t="s">
         <v>346</v>
       </c>
-      <c r="F32" s="157"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="157"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="140"/>
       <c r="I32" s="104" t="s">
         <v>57</v>
       </c>
@@ -4938,12 +4883,12 @@
       <c r="D33" s="96" t="s">
         <v>278</v>
       </c>
-      <c r="E33" s="160" t="s">
+      <c r="E33" s="146" t="s">
         <v>347</v>
       </c>
-      <c r="F33" s="161"/>
-      <c r="G33" s="161"/>
-      <c r="H33" s="162"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
+      <c r="H33" s="148"/>
       <c r="I33" s="104" t="s">
         <v>60</v>
       </c>
@@ -4973,12 +4918,12 @@
       <c r="D34" s="96" t="s">
         <v>280</v>
       </c>
-      <c r="E34" s="160" t="s">
+      <c r="E34" s="146" t="s">
         <v>348</v>
       </c>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="162"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="148"/>
       <c r="I34" s="104" t="s">
         <v>60</v>
       </c>
@@ -5008,12 +4953,12 @@
       <c r="D35" s="96" t="s">
         <v>281</v>
       </c>
-      <c r="E35" s="160" t="s">
+      <c r="E35" s="146" t="s">
         <v>349</v>
       </c>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="162"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="148"/>
       <c r="I35" s="104" t="s">
         <v>65</v>
       </c>
@@ -5043,12 +4988,12 @@
       <c r="D36" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="E36" s="160" t="s">
+      <c r="E36" s="146" t="s">
         <v>350</v>
       </c>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="162"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="148"/>
       <c r="I36" s="104" t="s">
         <v>35</v>
       </c>
@@ -5075,13 +5020,13 @@
       <c r="C37" s="30">
         <v>2</v>
       </c>
-      <c r="D37" s="163" t="s">
+      <c r="D37" s="144" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="164"/>
-      <c r="F37" s="164"/>
-      <c r="G37" s="164"/>
-      <c r="H37" s="164"/>
+      <c r="E37" s="145"/>
+      <c r="F37" s="145"/>
+      <c r="G37" s="145"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="59"/>
       <c r="J37" s="60"/>
       <c r="K37" s="60"/>
@@ -5096,15 +5041,15 @@
       <c r="C38" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="137" t="s">
+      <c r="D38" s="129" t="s">
         <v>284</v>
       </c>
-      <c r="E38" s="157" t="s">
+      <c r="E38" s="140" t="s">
         <v>351</v>
       </c>
-      <c r="F38" s="157"/>
-      <c r="G38" s="157"/>
-      <c r="H38" s="157"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="140"/>
       <c r="I38" s="104" t="s">
         <v>71</v>
       </c>
@@ -5131,15 +5076,15 @@
       <c r="C39" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="138" t="s">
+      <c r="D39" s="130" t="s">
         <v>285</v>
       </c>
-      <c r="E39" s="165" t="s">
+      <c r="E39" s="149" t="s">
         <v>352</v>
       </c>
-      <c r="F39" s="165"/>
-      <c r="G39" s="165"/>
-      <c r="H39" s="165"/>
+      <c r="F39" s="149"/>
+      <c r="G39" s="149"/>
+      <c r="H39" s="149"/>
       <c r="I39" s="104" t="s">
         <v>35</v>
       </c>
@@ -5166,15 +5111,15 @@
       <c r="C40" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="137" t="s">
+      <c r="D40" s="129" t="s">
         <v>289</v>
       </c>
-      <c r="E40" s="157" t="s">
+      <c r="E40" s="140" t="s">
         <v>353</v>
       </c>
-      <c r="F40" s="157"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="157"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="140"/>
       <c r="I40" s="104" t="s">
         <v>75</v>
       </c>
@@ -5201,15 +5146,15 @@
       <c r="C41" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="137" t="s">
+      <c r="D41" s="129" t="s">
         <v>290</v>
       </c>
-      <c r="E41" s="157" t="s">
+      <c r="E41" s="140" t="s">
         <v>354</v>
       </c>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="140"/>
       <c r="I41" s="104" t="s">
         <v>75</v>
       </c>
@@ -5236,15 +5181,15 @@
       <c r="C42" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="137" t="s">
+      <c r="D42" s="129" t="s">
         <v>291</v>
       </c>
-      <c r="E42" s="157" t="s">
+      <c r="E42" s="140" t="s">
         <v>355</v>
       </c>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="140"/>
       <c r="I42" s="104" t="s">
         <v>75</v>
       </c>
@@ -5271,15 +5216,15 @@
       <c r="C43" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="D43" s="137" t="s">
+      <c r="D43" s="129" t="s">
         <v>292</v>
       </c>
-      <c r="E43" s="157" t="s">
+      <c r="E43" s="140" t="s">
         <v>356</v>
       </c>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="140"/>
       <c r="I43" s="104" t="s">
         <v>81</v>
       </c>
@@ -5306,15 +5251,15 @@
       <c r="C44" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="137" t="s">
+      <c r="D44" s="129" t="s">
         <v>293</v>
       </c>
-      <c r="E44" s="157" t="s">
+      <c r="E44" s="140" t="s">
         <v>357</v>
       </c>
-      <c r="F44" s="157"/>
-      <c r="G44" s="157"/>
-      <c r="H44" s="157"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="140"/>
       <c r="I44" s="104" t="s">
         <v>84</v>
       </c>
@@ -5341,15 +5286,15 @@
       <c r="C45" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="137" t="s">
+      <c r="D45" s="129" t="s">
         <v>294</v>
       </c>
-      <c r="E45" s="157" t="s">
+      <c r="E45" s="140" t="s">
         <v>358</v>
       </c>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="157"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="140"/>
       <c r="I45" s="104" t="s">
         <v>84</v>
       </c>
@@ -5376,15 +5321,15 @@
       <c r="C46" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="137" t="s">
+      <c r="D46" s="129" t="s">
         <v>295</v>
       </c>
-      <c r="E46" s="157" t="s">
+      <c r="E46" s="140" t="s">
         <v>359</v>
       </c>
-      <c r="F46" s="157"/>
-      <c r="G46" s="157"/>
-      <c r="H46" s="157"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="140"/>
       <c r="I46" s="104" t="s">
         <v>84</v>
       </c>
@@ -5411,15 +5356,15 @@
       <c r="C47" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="137" t="s">
+      <c r="D47" s="129" t="s">
         <v>296</v>
       </c>
-      <c r="E47" s="157" t="s">
+      <c r="E47" s="140" t="s">
         <v>360</v>
       </c>
-      <c r="F47" s="157"/>
-      <c r="G47" s="157"/>
-      <c r="H47" s="157"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="140"/>
       <c r="I47" s="104" t="s">
         <v>84</v>
       </c>
@@ -5443,21 +5388,21 @@
     <row r="48" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="168" t="s">
+      <c r="C48" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="169"/>
-      <c r="E48" s="169"/>
-      <c r="F48" s="169"/>
-      <c r="G48" s="169"/>
-      <c r="H48" s="169"/>
-      <c r="I48" s="155"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="139"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="136"/>
       <c r="J48" s="64"/>
       <c r="K48" s="64"/>
       <c r="L48" s="64"/>
       <c r="M48" s="65">
         <f>SUM(M12:M47)</f>
-        <v>171623.40700000004</v>
+        <v>189275.65900000001</v>
       </c>
       <c r="N48" s="56"/>
       <c r="Q48" s="4"/>
@@ -5465,22 +5410,22 @@
     <row r="49" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="166" t="s">
+      <c r="C49" s="143" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="154"/>
-      <c r="E49" s="154"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="154"/>
-      <c r="I49" s="155"/>
-      <c r="J49" s="170" t="s">
+      <c r="D49" s="135"/>
+      <c r="E49" s="135"/>
+      <c r="F49" s="135"/>
+      <c r="G49" s="135"/>
+      <c r="H49" s="135"/>
+      <c r="I49" s="136"/>
+      <c r="J49" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="K49" s="154"/>
-      <c r="L49" s="154"/>
-      <c r="M49" s="154"/>
-      <c r="N49" s="155"/>
+      <c r="K49" s="135"/>
+      <c r="L49" s="135"/>
+      <c r="M49" s="135"/>
+      <c r="N49" s="136"/>
       <c r="Q49" s="4"/>
     </row>
     <row r="50" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5493,49 +5438,49 @@
       <c r="G50" s="67"/>
       <c r="H50" s="68"/>
       <c r="I50" s="69"/>
-      <c r="J50" s="170" t="s">
+      <c r="J50" s="141" t="s">
         <v>94</v>
       </c>
-      <c r="K50" s="154"/>
-      <c r="L50" s="154"/>
-      <c r="M50" s="154"/>
-      <c r="N50" s="155"/>
+      <c r="K50" s="135"/>
+      <c r="L50" s="135"/>
+      <c r="M50" s="135"/>
+      <c r="N50" s="136"/>
       <c r="Q50" s="4"/>
     </row>
     <row r="51" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="171" t="s">
+      <c r="C51" s="142" t="s">
         <v>95</v>
       </c>
-      <c r="D51" s="154"/>
-      <c r="E51" s="154"/>
-      <c r="F51" s="154"/>
-      <c r="G51" s="154"/>
-      <c r="H51" s="154"/>
-      <c r="I51" s="154"/>
-      <c r="J51" s="154"/>
-      <c r="K51" s="154"/>
-      <c r="L51" s="154"/>
-      <c r="M51" s="154"/>
-      <c r="N51" s="155"/>
+      <c r="D51" s="135"/>
+      <c r="E51" s="135"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="135"/>
+      <c r="H51" s="135"/>
+      <c r="I51" s="135"/>
+      <c r="J51" s="135"/>
+      <c r="K51" s="135"/>
+      <c r="L51" s="135"/>
+      <c r="M51" s="135"/>
+      <c r="N51" s="136"/>
       <c r="Q51" s="4"/>
     </row>
     <row r="52" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="167"/>
-      <c r="D52" s="154"/>
-      <c r="E52" s="154"/>
-      <c r="F52" s="154"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="154"/>
-      <c r="I52" s="154"/>
-      <c r="J52" s="154"/>
-      <c r="K52" s="154"/>
-      <c r="L52" s="154"/>
-      <c r="M52" s="154"/>
-      <c r="N52" s="155"/>
+      <c r="C52" s="134"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
+      <c r="I52" s="135"/>
+      <c r="J52" s="135"/>
+      <c r="K52" s="135"/>
+      <c r="L52" s="135"/>
+      <c r="M52" s="135"/>
+      <c r="N52" s="136"/>
       <c r="Q52" s="4"/>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5575,10 +5520,10 @@
       <c r="I54" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="J54" s="153" t="s">
+      <c r="J54" s="137" t="s">
         <v>101</v>
       </c>
-      <c r="K54" s="155"/>
+      <c r="K54" s="136"/>
       <c r="L54" s="71"/>
       <c r="M54" s="71"/>
       <c r="N54" s="71"/>
@@ -21668,31 +21613,12 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C52:N52"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="C48:I48"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="J49:N49"/>
-    <mergeCell ref="J50:N50"/>
-    <mergeCell ref="C51:N51"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="C49:I49"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="N24:N26"/>
     <mergeCell ref="N27:N29"/>
     <mergeCell ref="B6:C6"/>
@@ -21709,12 +21635,31 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="N15:N17"/>
     <mergeCell ref="N18:N20"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="C49:I49"/>
+    <mergeCell ref="C52:N52"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="C48:I48"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="J49:N49"/>
+    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="C51:N51"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="60" orientation="landscape"/>
@@ -21730,7 +21675,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:T963"/>
+  <dimension ref="A1:T945"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
@@ -21778,12 +21723,12 @@
       <c r="M1" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="N1" s="136" t="s">
+      <c r="N1" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
       <c r="R1" s="72"/>
       <c r="S1" s="72"/>
     </row>
@@ -21898,7 +21843,7 @@
       <c r="A4" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="125" t="s">
         <v>150</v>
       </c>
       <c r="C4" s="117">
@@ -21928,25 +21873,25 @@
       <c r="I4" s="120">
         <v>1</v>
       </c>
-      <c r="J4" s="172">
-        <v>141509</v>
-      </c>
-      <c r="K4" s="172">
+      <c r="J4" s="131">
+        <v>183910</v>
+      </c>
+      <c r="K4" s="131">
+        <v>1</v>
+      </c>
+      <c r="L4" s="131">
         <v>0</v>
       </c>
-      <c r="L4" s="172">
-        <v>0</v>
-      </c>
-      <c r="M4" s="172">
-        <v>41401</v>
+      <c r="M4" s="131">
+        <v>20282</v>
       </c>
       <c r="N4" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>182910</v>
+        <v>204191</v>
       </c>
       <c r="O4" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>182910</v>
+        <v>204191</v>
       </c>
       <c r="P4" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -21954,7 +21899,7 @@
       </c>
       <c r="Q4" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>109746</v>
+        <v>122514.59999999999</v>
       </c>
       <c r="R4" s="122" t="s">
         <v>122</v>
@@ -21968,7 +21913,7 @@
       <c r="A5" s="115" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="125" t="s">
         <v>151</v>
       </c>
       <c r="C5" s="117">
@@ -21998,25 +21943,25 @@
       <c r="I5" s="120">
         <v>1</v>
       </c>
-      <c r="J5" s="172">
-        <v>9</v>
-      </c>
-      <c r="K5" s="172">
+      <c r="J5" s="131">
+        <v>110</v>
+      </c>
+      <c r="K5" s="131">
         <v>0</v>
       </c>
-      <c r="L5" s="172">
+      <c r="L5" s="131">
         <v>0</v>
       </c>
-      <c r="M5" s="172">
-        <v>101</v>
+      <c r="M5" s="131">
+        <v>882</v>
       </c>
       <c r="N5" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="O5" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="P5" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -22024,7 +21969,7 @@
       </c>
       <c r="Q5" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>390.5</v>
+        <v>3521.6</v>
       </c>
       <c r="R5" s="122" t="s">
         <v>124</v>
@@ -22038,7 +21983,7 @@
       <c r="A6" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="125" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="117">
@@ -22068,16 +22013,16 @@
       <c r="I6" s="120">
         <v>1.113</v>
       </c>
-      <c r="J6" s="172">
+      <c r="J6" s="131">
         <v>0</v>
       </c>
-      <c r="K6" s="172">
+      <c r="K6" s="131">
         <v>0</v>
       </c>
-      <c r="L6" s="172">
+      <c r="L6" s="131">
         <v>0</v>
       </c>
-      <c r="M6" s="172">
+      <c r="M6" s="131">
         <v>0</v>
       </c>
       <c r="N6" s="119">
@@ -22108,7 +22053,7 @@
       <c r="A7" s="115" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="125" t="s">
         <v>361</v>
       </c>
       <c r="C7" s="117">
@@ -22138,25 +22083,25 @@
       <c r="I7" s="120">
         <v>0.505</v>
       </c>
-      <c r="J7" s="172">
+      <c r="J7" s="131">
         <v>1014</v>
       </c>
-      <c r="K7" s="172">
+      <c r="K7" s="131">
         <v>0</v>
       </c>
-      <c r="L7" s="172">
+      <c r="L7" s="131">
         <v>0</v>
       </c>
-      <c r="M7" s="172">
-        <v>0</v>
+      <c r="M7" s="131">
+        <v>5784</v>
       </c>
       <c r="N7" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>1014</v>
+        <v>6798</v>
       </c>
       <c r="O7" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>512.07000000000005</v>
+        <v>3432.9900000000002</v>
       </c>
       <c r="P7" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -22164,7 +22109,7 @@
       </c>
       <c r="Q7" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>307.24200000000002</v>
+        <v>2059.7939999999999</v>
       </c>
       <c r="R7" s="122" t="s">
         <v>122</v>
@@ -22178,7 +22123,7 @@
       <c r="A8" s="115" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="125" t="s">
         <v>152</v>
       </c>
       <c r="C8" s="117">
@@ -22208,16 +22153,16 @@
       <c r="I8" s="120">
         <v>1</v>
       </c>
-      <c r="J8" s="172">
+      <c r="J8" s="131">
         <v>10338</v>
       </c>
-      <c r="K8" s="172">
+      <c r="K8" s="131">
         <v>0</v>
       </c>
-      <c r="L8" s="172">
+      <c r="L8" s="131">
         <v>0</v>
       </c>
-      <c r="M8" s="172">
+      <c r="M8" s="131">
         <v>0</v>
       </c>
       <c r="N8" s="119">
@@ -22248,7 +22193,7 @@
       <c r="A9" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="125" t="s">
         <v>131</v>
       </c>
       <c r="C9" s="117">
@@ -22278,16 +22223,16 @@
       <c r="I9" s="120">
         <v>1</v>
       </c>
-      <c r="J9" s="172">
+      <c r="J9" s="131">
         <v>17</v>
       </c>
-      <c r="K9" s="172">
+      <c r="K9" s="131">
         <v>0</v>
       </c>
-      <c r="L9" s="172">
+      <c r="L9" s="131">
         <v>0</v>
       </c>
-      <c r="M9" s="172">
+      <c r="M9" s="131">
         <v>0</v>
       </c>
       <c r="N9" s="119">
@@ -22318,7 +22263,7 @@
       <c r="A10" s="115" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="125" t="s">
         <v>140</v>
       </c>
       <c r="C10" s="117">
@@ -22348,16 +22293,16 @@
       <c r="I10" s="120">
         <v>1</v>
       </c>
-      <c r="J10" s="172">
+      <c r="J10" s="131">
         <v>0</v>
       </c>
-      <c r="K10" s="172">
+      <c r="K10" s="131">
         <v>0</v>
       </c>
-      <c r="L10" s="172">
+      <c r="L10" s="131">
         <v>0</v>
       </c>
-      <c r="M10" s="172">
+      <c r="M10" s="131">
         <v>0</v>
       </c>
       <c r="N10" s="119">
@@ -22388,7 +22333,7 @@
       <c r="A11" s="115" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="125" t="s">
         <v>380</v>
       </c>
       <c r="C11" s="117">
@@ -22418,16 +22363,16 @@
       <c r="I11" s="120">
         <v>1</v>
       </c>
-      <c r="J11" s="172">
+      <c r="J11" s="131">
         <v>5193</v>
       </c>
-      <c r="K11" s="172">
+      <c r="K11" s="131">
         <v>0</v>
       </c>
-      <c r="L11" s="172">
+      <c r="L11" s="131">
         <v>0</v>
       </c>
-      <c r="M11" s="172">
+      <c r="M11" s="131">
         <v>0</v>
       </c>
       <c r="N11" s="119">
@@ -22458,7 +22403,7 @@
       <c r="A12" s="115" t="s">
         <v>340</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="125" t="s">
         <v>385</v>
       </c>
       <c r="C12" s="117">
@@ -22488,16 +22433,16 @@
       <c r="I12" s="116">
         <v>0.25</v>
       </c>
-      <c r="J12" s="172">
+      <c r="J12" s="131">
         <v>4309</v>
       </c>
-      <c r="K12" s="172">
+      <c r="K12" s="131">
         <v>0</v>
       </c>
-      <c r="L12" s="172">
+      <c r="L12" s="131">
         <v>0</v>
       </c>
-      <c r="M12" s="172">
+      <c r="M12" s="131">
         <v>0</v>
       </c>
       <c r="N12" s="119">
@@ -22519,929 +22464,387 @@
       <c r="R12" s="116" t="s">
         <v>129</v>
       </c>
-      <c r="S12" s="125" t="s">
+      <c r="S12" s="124" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="115"/>
-      <c r="B13" s="132"/>
-      <c r="C13" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D13" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F13" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="119" t="str">
-        <f>IFERROR( Consolidado!$D13*Consolidado!$E13*Consolidado!$F13, "")</f>
-        <v/>
-      </c>
-      <c r="H13" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O13" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P13" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R13" s="116"/>
-      <c r="S13" s="125"/>
-    </row>
-    <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
-      <c r="B14" s="132"/>
-      <c r="C14" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D14" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F14" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="119" t="str">
-        <f>IFERROR( Consolidado!$D14*Consolidado!$E14*Consolidado!$F14, "")</f>
-        <v/>
-      </c>
-      <c r="H14" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O14" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P14" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R14" s="116"/>
-      <c r="S14" s="125"/>
-    </row>
-    <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="115"/>
-      <c r="B15" s="132"/>
-      <c r="C15" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D15" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F15" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="119" t="str">
-        <f>IFERROR( Consolidado!$D15*Consolidado!$E15*Consolidado!$F15, "")</f>
-        <v/>
-      </c>
-      <c r="H15" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="124">
-        <v>22</v>
-      </c>
-      <c r="N15" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O15" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P15" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R15" s="116"/>
-      <c r="S15" s="125"/>
-    </row>
-    <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="115"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D16" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E16" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F16" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="119" t="str">
-        <f>IFERROR( Consolidado!$D16*Consolidado!$E16*Consolidado!$F16, "")</f>
-        <v/>
-      </c>
-      <c r="H16" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O16" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P16" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R16" s="116"/>
-      <c r="S16" s="125"/>
-    </row>
-    <row r="17" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="115"/>
-      <c r="B17" s="132"/>
-      <c r="C17" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D17" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E17" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F17" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="119" t="str">
-        <f>IFERROR( Consolidado!$D17*Consolidado!$E17*Consolidado!$F17, "")</f>
-        <v/>
-      </c>
-      <c r="H17" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I17" s="116"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O17" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P17" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R17" s="116"/>
-      <c r="S17" s="125"/>
-    </row>
-    <row r="18" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="115"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D18" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E18" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F18" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="119" t="str">
-        <f>IFERROR( Consolidado!$D18*Consolidado!$E18*Consolidado!$F18, "")</f>
-        <v/>
-      </c>
-      <c r="H18" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O18" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P18" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R18" s="116"/>
-      <c r="S18" s="125"/>
-    </row>
-    <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="115"/>
-      <c r="B19" s="132"/>
-      <c r="C19" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D19" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E19" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F19" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="119" t="str">
-        <f>IFERROR( Consolidado!$D19*Consolidado!$E19*Consolidado!$F19, "")</f>
-        <v/>
-      </c>
-      <c r="H19" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="124"/>
-      <c r="N19" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O19" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P19" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R19" s="116"/>
-      <c r="S19" s="125"/>
-    </row>
-    <row r="20" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="115"/>
-      <c r="B20" s="132"/>
-      <c r="C20" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D20" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E20" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F20" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G20" s="119" t="str">
-        <f>IFERROR( Consolidado!$D20*Consolidado!$E20*Consolidado!$F20, "")</f>
-        <v/>
-      </c>
-      <c r="H20" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O20" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P20" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R20" s="116"/>
-      <c r="S20" s="125"/>
-    </row>
-    <row r="21" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="115"/>
-      <c r="B21" s="132"/>
-      <c r="C21" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D21" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E21" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F21" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G21" s="119" t="str">
-        <f>IFERROR( Consolidado!$D21*Consolidado!$E21*Consolidado!$F21, "")</f>
-        <v/>
-      </c>
-      <c r="H21" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O21" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P21" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R21" s="116"/>
-      <c r="S21" s="125"/>
-    </row>
-    <row r="22" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="115"/>
-      <c r="B22" s="132"/>
-      <c r="C22" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D22" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E22" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F22" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="119" t="str">
-        <f>IFERROR( Consolidado!$D22*Consolidado!$E22*Consolidado!$F22, "")</f>
-        <v/>
-      </c>
-      <c r="H22" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="124"/>
-      <c r="N22" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O22" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P22" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R22" s="116"/>
-      <c r="S22" s="125"/>
-    </row>
-    <row r="23" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
-      <c r="B23" s="132"/>
-      <c r="C23" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D23" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E23" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F23" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="119" t="str">
-        <f>IFERROR( Consolidado!$D23*Consolidado!$E23*Consolidado!$F23, "")</f>
-        <v/>
-      </c>
-      <c r="H23" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I23" s="116"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O23" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P23" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q23" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R23" s="116"/>
-      <c r="S23" s="125"/>
+    <row r="13" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="72"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+    </row>
+    <row r="14" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+    </row>
+    <row r="15" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="72"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+    </row>
+    <row r="16" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="72"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="76"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+    </row>
+    <row r="17" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="72"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+    </row>
+    <row r="18" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="72"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+    </row>
+    <row r="19" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="72"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+    </row>
+    <row r="20" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="72"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+    </row>
+    <row r="21" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="72"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+    </row>
+    <row r="22" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="72"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+    </row>
+    <row r="23" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="72"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
     </row>
     <row r="24" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="115"/>
-      <c r="B24" s="132"/>
-      <c r="C24" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D24" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E24" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F24" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="119" t="str">
-        <f>IFERROR( Consolidado!$D24*Consolidado!$E24*Consolidado!$F24, "")</f>
-        <v/>
-      </c>
-      <c r="H24" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O24" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P24" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R24" s="116"/>
-      <c r="S24" s="125"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
     </row>
     <row r="25" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="115"/>
-      <c r="B25" s="132"/>
-      <c r="C25" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D25" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E25" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F25" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G25" s="119" t="str">
-        <f>IFERROR( Consolidado!$D25*Consolidado!$E25*Consolidado!$F25, "")</f>
-        <v/>
-      </c>
-      <c r="H25" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I25" s="116"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="124"/>
-      <c r="N25" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O25" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P25" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R25" s="116"/>
-      <c r="S25" s="125"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
     </row>
     <row r="26" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="115"/>
-      <c r="B26" s="132"/>
-      <c r="C26" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D26" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E26" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F26" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G26" s="119" t="str">
-        <f>IFERROR( Consolidado!$D26*Consolidado!$E26*Consolidado!$F26, "")</f>
-        <v/>
-      </c>
-      <c r="H26" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O26" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P26" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R26" s="116"/>
-      <c r="S26" s="125"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
     </row>
     <row r="27" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
-      <c r="B27" s="132"/>
-      <c r="C27" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D27" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E27" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F27" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G27" s="119" t="str">
-        <f>IFERROR( Consolidado!$D27*Consolidado!$E27*Consolidado!$F27, "")</f>
-        <v/>
-      </c>
-      <c r="H27" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O27" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P27" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R27" s="116"/>
-      <c r="S27" s="125"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
     </row>
     <row r="28" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="115"/>
-      <c r="B28" s="132"/>
-      <c r="C28" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D28" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E28" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F28" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G28" s="119" t="str">
-        <f>IFERROR( Consolidado!$D28*Consolidado!$E28*Consolidado!$F28, "")</f>
-        <v/>
-      </c>
-      <c r="H28" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="124"/>
-      <c r="N28" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O28" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P28" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R28" s="116"/>
-      <c r="S28" s="125"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
     </row>
     <row r="29" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="115"/>
-      <c r="B29" s="132"/>
-      <c r="C29" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D29" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E29" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F29" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G29" s="119" t="str">
-        <f>IFERROR( Consolidado!$D29*Consolidado!$E29*Consolidado!$F29, "")</f>
-        <v/>
-      </c>
-      <c r="H29" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="124"/>
-      <c r="N29" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O29" s="119" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P29" s="121" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q29" s="121" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R29" s="116"/>
-      <c r="S29" s="125"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
     </row>
     <row r="30" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="126"/>
-      <c r="B30" s="133"/>
-      <c r="C30" s="117" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[[MEDIDAS CONTRATO]:[Ø]],2,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="D30" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],3,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="E30" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],4,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="F30" s="118" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[MEDIDAS CONTRATO]],MedidasContrato[],5,0),"N/A"))</f>
-        <v/>
-      </c>
-      <c r="G30" s="119" t="str">
-        <f>IFERROR( Consolidado!$D30*Consolidado!$E30*Consolidado!$F30, "")</f>
-        <v/>
-      </c>
-      <c r="H30" s="119" t="str">
-        <f>IFERROR( IF(ConsolidadoRJ[[#This Row],[cm³ = V1]]="","",ConsolidadoRJ[[#This Row],[cm³ = V1]]/ConsolidadoRJ[[#This Row],[FC = V1/V2]]), "")</f>
-        <v/>
-      </c>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="128" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v/>
-      </c>
-      <c r="O30" s="128" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v/>
-      </c>
-      <c r="P30" s="130" t="str">
-        <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
-        <v/>
-      </c>
-      <c r="Q30" s="130" t="str">
-        <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v/>
-      </c>
-      <c r="R30" s="127"/>
-      <c r="S30" s="131"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
     </row>
     <row r="31" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="72"/>
@@ -23502,7 +22905,7 @@
       <c r="N33" s="72"/>
       <c r="O33" s="72"/>
       <c r="P33" s="72"/>
-      <c r="Q33" s="76"/>
+      <c r="Q33" s="72"/>
       <c r="R33" s="72"/>
       <c r="S33" s="72"/>
     </row>
@@ -23523,7 +22926,7 @@
       <c r="N34" s="72"/>
       <c r="O34" s="72"/>
       <c r="P34" s="72"/>
-      <c r="Q34" s="76"/>
+      <c r="Q34" s="72"/>
       <c r="R34" s="72"/>
       <c r="S34" s="72"/>
     </row>
@@ -26817,7 +26220,6 @@
       <c r="K191" s="72"/>
       <c r="L191" s="72"/>
       <c r="M191" s="72"/>
-      <c r="N191" s="72"/>
       <c r="O191" s="72"/>
       <c r="P191" s="72"/>
       <c r="Q191" s="72"/>
@@ -26838,7 +26240,6 @@
       <c r="K192" s="72"/>
       <c r="L192" s="72"/>
       <c r="M192" s="72"/>
-      <c r="N192" s="72"/>
       <c r="O192" s="72"/>
       <c r="P192" s="72"/>
       <c r="Q192" s="72"/>
@@ -26859,7 +26260,6 @@
       <c r="K193" s="72"/>
       <c r="L193" s="72"/>
       <c r="M193" s="72"/>
-      <c r="N193" s="72"/>
       <c r="O193" s="72"/>
       <c r="P193" s="72"/>
       <c r="Q193" s="72"/>
@@ -26880,7 +26280,6 @@
       <c r="K194" s="72"/>
       <c r="L194" s="72"/>
       <c r="M194" s="72"/>
-      <c r="N194" s="72"/>
       <c r="O194" s="72"/>
       <c r="P194" s="72"/>
       <c r="Q194" s="72"/>
@@ -26901,7 +26300,6 @@
       <c r="K195" s="72"/>
       <c r="L195" s="72"/>
       <c r="M195" s="72"/>
-      <c r="N195" s="72"/>
       <c r="O195" s="72"/>
       <c r="P195" s="72"/>
       <c r="Q195" s="72"/>
@@ -26922,7 +26320,6 @@
       <c r="K196" s="72"/>
       <c r="L196" s="72"/>
       <c r="M196" s="72"/>
-      <c r="N196" s="72"/>
       <c r="O196" s="72"/>
       <c r="P196" s="72"/>
       <c r="Q196" s="72"/>
@@ -26943,7 +26340,6 @@
       <c r="K197" s="72"/>
       <c r="L197" s="72"/>
       <c r="M197" s="72"/>
-      <c r="N197" s="72"/>
       <c r="O197" s="72"/>
       <c r="P197" s="72"/>
       <c r="Q197" s="72"/>
@@ -26964,7 +26360,6 @@
       <c r="K198" s="72"/>
       <c r="L198" s="72"/>
       <c r="M198" s="72"/>
-      <c r="N198" s="72"/>
       <c r="O198" s="72"/>
       <c r="P198" s="72"/>
       <c r="Q198" s="72"/>
@@ -26985,7 +26380,6 @@
       <c r="K199" s="72"/>
       <c r="L199" s="72"/>
       <c r="M199" s="72"/>
-      <c r="N199" s="72"/>
       <c r="O199" s="72"/>
       <c r="P199" s="72"/>
       <c r="Q199" s="72"/>
@@ -27006,7 +26400,6 @@
       <c r="K200" s="72"/>
       <c r="L200" s="72"/>
       <c r="M200" s="72"/>
-      <c r="N200" s="72"/>
       <c r="O200" s="72"/>
       <c r="P200" s="72"/>
       <c r="Q200" s="72"/>
@@ -27027,7 +26420,6 @@
       <c r="K201" s="72"/>
       <c r="L201" s="72"/>
       <c r="M201" s="72"/>
-      <c r="N201" s="72"/>
       <c r="O201" s="72"/>
       <c r="P201" s="72"/>
       <c r="Q201" s="72"/>
@@ -27048,7 +26440,6 @@
       <c r="K202" s="72"/>
       <c r="L202" s="72"/>
       <c r="M202" s="72"/>
-      <c r="N202" s="72"/>
       <c r="O202" s="72"/>
       <c r="P202" s="72"/>
       <c r="Q202" s="72"/>
@@ -27069,7 +26460,6 @@
       <c r="K203" s="72"/>
       <c r="L203" s="72"/>
       <c r="M203" s="72"/>
-      <c r="N203" s="72"/>
       <c r="O203" s="72"/>
       <c r="P203" s="72"/>
       <c r="Q203" s="72"/>
@@ -27090,7 +26480,6 @@
       <c r="K204" s="72"/>
       <c r="L204" s="72"/>
       <c r="M204" s="72"/>
-      <c r="N204" s="72"/>
       <c r="O204" s="72"/>
       <c r="P204" s="72"/>
       <c r="Q204" s="72"/>
@@ -27111,7 +26500,6 @@
       <c r="K205" s="72"/>
       <c r="L205" s="72"/>
       <c r="M205" s="72"/>
-      <c r="N205" s="72"/>
       <c r="O205" s="72"/>
       <c r="P205" s="72"/>
       <c r="Q205" s="72"/>
@@ -27132,7 +26520,6 @@
       <c r="K206" s="72"/>
       <c r="L206" s="72"/>
       <c r="M206" s="72"/>
-      <c r="N206" s="72"/>
       <c r="O206" s="72"/>
       <c r="P206" s="72"/>
       <c r="Q206" s="72"/>
@@ -27153,7 +26540,6 @@
       <c r="K207" s="72"/>
       <c r="L207" s="72"/>
       <c r="M207" s="72"/>
-      <c r="N207" s="72"/>
       <c r="O207" s="72"/>
       <c r="P207" s="72"/>
       <c r="Q207" s="72"/>
@@ -27174,7 +26560,6 @@
       <c r="K208" s="72"/>
       <c r="L208" s="72"/>
       <c r="M208" s="72"/>
-      <c r="N208" s="72"/>
       <c r="O208" s="72"/>
       <c r="P208" s="72"/>
       <c r="Q208" s="72"/>
@@ -41501,7 +40886,7 @@
       <c r="R924" s="72"/>
       <c r="S924" s="72"/>
     </row>
-    <row r="925" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A925" s="72"/>
       <c r="B925" s="72"/>
       <c r="C925" s="72"/>
@@ -41521,7 +40906,7 @@
       <c r="R925" s="72"/>
       <c r="S925" s="72"/>
     </row>
-    <row r="926" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A926" s="72"/>
       <c r="B926" s="72"/>
       <c r="C926" s="72"/>
@@ -41541,7 +40926,7 @@
       <c r="R926" s="72"/>
       <c r="S926" s="72"/>
     </row>
-    <row r="927" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A927" s="72"/>
       <c r="B927" s="72"/>
       <c r="C927" s="72"/>
@@ -41561,7 +40946,7 @@
       <c r="R927" s="72"/>
       <c r="S927" s="72"/>
     </row>
-    <row r="928" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A928" s="72"/>
       <c r="B928" s="72"/>
       <c r="C928" s="72"/>
@@ -41581,7 +40966,7 @@
       <c r="R928" s="72"/>
       <c r="S928" s="72"/>
     </row>
-    <row r="929" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A929" s="72"/>
       <c r="B929" s="72"/>
       <c r="C929" s="72"/>
@@ -41601,7 +40986,7 @@
       <c r="R929" s="72"/>
       <c r="S929" s="72"/>
     </row>
-    <row r="930" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A930" s="72"/>
       <c r="B930" s="72"/>
       <c r="C930" s="72"/>
@@ -41621,7 +41006,7 @@
       <c r="R930" s="72"/>
       <c r="S930" s="72"/>
     </row>
-    <row r="931" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A931" s="72"/>
       <c r="B931" s="72"/>
       <c r="C931" s="72"/>
@@ -41641,7 +41026,7 @@
       <c r="R931" s="72"/>
       <c r="S931" s="72"/>
     </row>
-    <row r="932" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A932" s="72"/>
       <c r="B932" s="72"/>
       <c r="C932" s="72"/>
@@ -41661,7 +41046,7 @@
       <c r="R932" s="72"/>
       <c r="S932" s="72"/>
     </row>
-    <row r="933" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A933" s="72"/>
       <c r="B933" s="72"/>
       <c r="C933" s="72"/>
@@ -41681,7 +41066,7 @@
       <c r="R933" s="72"/>
       <c r="S933" s="72"/>
     </row>
-    <row r="934" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A934" s="72"/>
       <c r="B934" s="72"/>
       <c r="C934" s="72"/>
@@ -41701,7 +41086,7 @@
       <c r="R934" s="72"/>
       <c r="S934" s="72"/>
     </row>
-    <row r="935" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A935" s="72"/>
       <c r="B935" s="72"/>
       <c r="C935" s="72"/>
@@ -41721,7 +41106,7 @@
       <c r="R935" s="72"/>
       <c r="S935" s="72"/>
     </row>
-    <row r="936" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A936" s="72"/>
       <c r="B936" s="72"/>
       <c r="C936" s="72"/>
@@ -41741,7 +41126,7 @@
       <c r="R936" s="72"/>
       <c r="S936" s="72"/>
     </row>
-    <row r="937" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A937" s="72"/>
       <c r="B937" s="72"/>
       <c r="C937" s="72"/>
@@ -41761,7 +41146,7 @@
       <c r="R937" s="72"/>
       <c r="S937" s="72"/>
     </row>
-    <row r="938" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A938" s="72"/>
       <c r="B938" s="72"/>
       <c r="C938" s="72"/>
@@ -41781,7 +41166,7 @@
       <c r="R938" s="72"/>
       <c r="S938" s="72"/>
     </row>
-    <row r="939" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A939" s="72"/>
       <c r="B939" s="72"/>
       <c r="C939" s="72"/>
@@ -41801,7 +41186,7 @@
       <c r="R939" s="72"/>
       <c r="S939" s="72"/>
     </row>
-    <row r="940" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A940" s="72"/>
       <c r="B940" s="72"/>
       <c r="C940" s="72"/>
@@ -41821,7 +41206,7 @@
       <c r="R940" s="72"/>
       <c r="S940" s="72"/>
     </row>
-    <row r="941" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A941" s="72"/>
       <c r="B941" s="72"/>
       <c r="C941" s="72"/>
@@ -41841,7 +41226,7 @@
       <c r="R941" s="72"/>
       <c r="S941" s="72"/>
     </row>
-    <row r="942" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A942" s="72"/>
       <c r="B942" s="72"/>
       <c r="C942" s="72"/>
@@ -41921,369 +41306,9 @@
       <c r="R945" s="72"/>
       <c r="S945" s="72"/>
     </row>
-    <row r="946" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A946" s="72"/>
-      <c r="B946" s="72"/>
-      <c r="C946" s="72"/>
-      <c r="D946" s="72"/>
-      <c r="E946" s="72"/>
-      <c r="F946" s="72"/>
-      <c r="G946" s="72"/>
-      <c r="H946" s="72"/>
-      <c r="I946" s="72"/>
-      <c r="J946" s="72"/>
-      <c r="K946" s="72"/>
-      <c r="L946" s="72"/>
-      <c r="M946" s="72"/>
-      <c r="O946" s="72"/>
-      <c r="P946" s="72"/>
-      <c r="Q946" s="72"/>
-      <c r="R946" s="72"/>
-      <c r="S946" s="72"/>
-    </row>
-    <row r="947" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A947" s="72"/>
-      <c r="B947" s="72"/>
-      <c r="C947" s="72"/>
-      <c r="D947" s="72"/>
-      <c r="E947" s="72"/>
-      <c r="F947" s="72"/>
-      <c r="G947" s="72"/>
-      <c r="H947" s="72"/>
-      <c r="I947" s="72"/>
-      <c r="J947" s="72"/>
-      <c r="K947" s="72"/>
-      <c r="L947" s="72"/>
-      <c r="M947" s="72"/>
-      <c r="O947" s="72"/>
-      <c r="P947" s="72"/>
-      <c r="Q947" s="72"/>
-      <c r="R947" s="72"/>
-      <c r="S947" s="72"/>
-    </row>
-    <row r="948" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A948" s="72"/>
-      <c r="B948" s="72"/>
-      <c r="C948" s="72"/>
-      <c r="D948" s="72"/>
-      <c r="E948" s="72"/>
-      <c r="F948" s="72"/>
-      <c r="G948" s="72"/>
-      <c r="H948" s="72"/>
-      <c r="I948" s="72"/>
-      <c r="J948" s="72"/>
-      <c r="K948" s="72"/>
-      <c r="L948" s="72"/>
-      <c r="M948" s="72"/>
-      <c r="O948" s="72"/>
-      <c r="P948" s="72"/>
-      <c r="Q948" s="72"/>
-      <c r="R948" s="72"/>
-      <c r="S948" s="72"/>
-    </row>
-    <row r="949" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A949" s="72"/>
-      <c r="B949" s="72"/>
-      <c r="C949" s="72"/>
-      <c r="D949" s="72"/>
-      <c r="E949" s="72"/>
-      <c r="F949" s="72"/>
-      <c r="G949" s="72"/>
-      <c r="H949" s="72"/>
-      <c r="I949" s="72"/>
-      <c r="J949" s="72"/>
-      <c r="K949" s="72"/>
-      <c r="L949" s="72"/>
-      <c r="M949" s="72"/>
-      <c r="O949" s="72"/>
-      <c r="P949" s="72"/>
-      <c r="Q949" s="72"/>
-      <c r="R949" s="72"/>
-      <c r="S949" s="72"/>
-    </row>
-    <row r="950" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A950" s="72"/>
-      <c r="B950" s="72"/>
-      <c r="C950" s="72"/>
-      <c r="D950" s="72"/>
-      <c r="E950" s="72"/>
-      <c r="F950" s="72"/>
-      <c r="G950" s="72"/>
-      <c r="H950" s="72"/>
-      <c r="I950" s="72"/>
-      <c r="J950" s="72"/>
-      <c r="K950" s="72"/>
-      <c r="L950" s="72"/>
-      <c r="M950" s="72"/>
-      <c r="O950" s="72"/>
-      <c r="P950" s="72"/>
-      <c r="Q950" s="72"/>
-      <c r="R950" s="72"/>
-      <c r="S950" s="72"/>
-    </row>
-    <row r="951" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A951" s="72"/>
-      <c r="B951" s="72"/>
-      <c r="C951" s="72"/>
-      <c r="D951" s="72"/>
-      <c r="E951" s="72"/>
-      <c r="F951" s="72"/>
-      <c r="G951" s="72"/>
-      <c r="H951" s="72"/>
-      <c r="I951" s="72"/>
-      <c r="J951" s="72"/>
-      <c r="K951" s="72"/>
-      <c r="L951" s="72"/>
-      <c r="M951" s="72"/>
-      <c r="O951" s="72"/>
-      <c r="P951" s="72"/>
-      <c r="Q951" s="72"/>
-      <c r="R951" s="72"/>
-      <c r="S951" s="72"/>
-    </row>
-    <row r="952" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A952" s="72"/>
-      <c r="B952" s="72"/>
-      <c r="C952" s="72"/>
-      <c r="D952" s="72"/>
-      <c r="E952" s="72"/>
-      <c r="F952" s="72"/>
-      <c r="G952" s="72"/>
-      <c r="H952" s="72"/>
-      <c r="I952" s="72"/>
-      <c r="J952" s="72"/>
-      <c r="K952" s="72"/>
-      <c r="L952" s="72"/>
-      <c r="M952" s="72"/>
-      <c r="O952" s="72"/>
-      <c r="P952" s="72"/>
-      <c r="Q952" s="72"/>
-      <c r="R952" s="72"/>
-      <c r="S952" s="72"/>
-    </row>
-    <row r="953" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A953" s="72"/>
-      <c r="B953" s="72"/>
-      <c r="C953" s="72"/>
-      <c r="D953" s="72"/>
-      <c r="E953" s="72"/>
-      <c r="F953" s="72"/>
-      <c r="G953" s="72"/>
-      <c r="H953" s="72"/>
-      <c r="I953" s="72"/>
-      <c r="J953" s="72"/>
-      <c r="K953" s="72"/>
-      <c r="L953" s="72"/>
-      <c r="M953" s="72"/>
-      <c r="O953" s="72"/>
-      <c r="P953" s="72"/>
-      <c r="Q953" s="72"/>
-      <c r="R953" s="72"/>
-      <c r="S953" s="72"/>
-    </row>
-    <row r="954" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A954" s="72"/>
-      <c r="B954" s="72"/>
-      <c r="C954" s="72"/>
-      <c r="D954" s="72"/>
-      <c r="E954" s="72"/>
-      <c r="F954" s="72"/>
-      <c r="G954" s="72"/>
-      <c r="H954" s="72"/>
-      <c r="I954" s="72"/>
-      <c r="J954" s="72"/>
-      <c r="K954" s="72"/>
-      <c r="L954" s="72"/>
-      <c r="M954" s="72"/>
-      <c r="O954" s="72"/>
-      <c r="P954" s="72"/>
-      <c r="Q954" s="72"/>
-      <c r="R954" s="72"/>
-      <c r="S954" s="72"/>
-    </row>
-    <row r="955" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A955" s="72"/>
-      <c r="B955" s="72"/>
-      <c r="C955" s="72"/>
-      <c r="D955" s="72"/>
-      <c r="E955" s="72"/>
-      <c r="F955" s="72"/>
-      <c r="G955" s="72"/>
-      <c r="H955" s="72"/>
-      <c r="I955" s="72"/>
-      <c r="J955" s="72"/>
-      <c r="K955" s="72"/>
-      <c r="L955" s="72"/>
-      <c r="M955" s="72"/>
-      <c r="O955" s="72"/>
-      <c r="P955" s="72"/>
-      <c r="Q955" s="72"/>
-      <c r="R955" s="72"/>
-      <c r="S955" s="72"/>
-    </row>
-    <row r="956" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A956" s="72"/>
-      <c r="B956" s="72"/>
-      <c r="C956" s="72"/>
-      <c r="D956" s="72"/>
-      <c r="E956" s="72"/>
-      <c r="F956" s="72"/>
-      <c r="G956" s="72"/>
-      <c r="H956" s="72"/>
-      <c r="I956" s="72"/>
-      <c r="J956" s="72"/>
-      <c r="K956" s="72"/>
-      <c r="L956" s="72"/>
-      <c r="M956" s="72"/>
-      <c r="O956" s="72"/>
-      <c r="P956" s="72"/>
-      <c r="Q956" s="72"/>
-      <c r="R956" s="72"/>
-      <c r="S956" s="72"/>
-    </row>
-    <row r="957" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A957" s="72"/>
-      <c r="B957" s="72"/>
-      <c r="C957" s="72"/>
-      <c r="D957" s="72"/>
-      <c r="E957" s="72"/>
-      <c r="F957" s="72"/>
-      <c r="G957" s="72"/>
-      <c r="H957" s="72"/>
-      <c r="I957" s="72"/>
-      <c r="J957" s="72"/>
-      <c r="K957" s="72"/>
-      <c r="L957" s="72"/>
-      <c r="M957" s="72"/>
-      <c r="O957" s="72"/>
-      <c r="P957" s="72"/>
-      <c r="Q957" s="72"/>
-      <c r="R957" s="72"/>
-      <c r="S957" s="72"/>
-    </row>
-    <row r="958" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A958" s="72"/>
-      <c r="B958" s="72"/>
-      <c r="C958" s="72"/>
-      <c r="D958" s="72"/>
-      <c r="E958" s="72"/>
-      <c r="F958" s="72"/>
-      <c r="G958" s="72"/>
-      <c r="H958" s="72"/>
-      <c r="I958" s="72"/>
-      <c r="J958" s="72"/>
-      <c r="K958" s="72"/>
-      <c r="L958" s="72"/>
-      <c r="M958" s="72"/>
-      <c r="O958" s="72"/>
-      <c r="P958" s="72"/>
-      <c r="Q958" s="72"/>
-      <c r="R958" s="72"/>
-      <c r="S958" s="72"/>
-    </row>
-    <row r="959" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A959" s="72"/>
-      <c r="B959" s="72"/>
-      <c r="C959" s="72"/>
-      <c r="D959" s="72"/>
-      <c r="E959" s="72"/>
-      <c r="F959" s="72"/>
-      <c r="G959" s="72"/>
-      <c r="H959" s="72"/>
-      <c r="I959" s="72"/>
-      <c r="J959" s="72"/>
-      <c r="K959" s="72"/>
-      <c r="L959" s="72"/>
-      <c r="M959" s="72"/>
-      <c r="O959" s="72"/>
-      <c r="P959" s="72"/>
-      <c r="Q959" s="72"/>
-      <c r="R959" s="72"/>
-      <c r="S959" s="72"/>
-    </row>
-    <row r="960" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A960" s="72"/>
-      <c r="B960" s="72"/>
-      <c r="C960" s="72"/>
-      <c r="D960" s="72"/>
-      <c r="E960" s="72"/>
-      <c r="F960" s="72"/>
-      <c r="G960" s="72"/>
-      <c r="H960" s="72"/>
-      <c r="I960" s="72"/>
-      <c r="J960" s="72"/>
-      <c r="K960" s="72"/>
-      <c r="L960" s="72"/>
-      <c r="M960" s="72"/>
-      <c r="O960" s="72"/>
-      <c r="P960" s="72"/>
-      <c r="Q960" s="72"/>
-      <c r="R960" s="72"/>
-      <c r="S960" s="72"/>
-    </row>
-    <row r="961" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A961" s="72"/>
-      <c r="B961" s="72"/>
-      <c r="C961" s="72"/>
-      <c r="D961" s="72"/>
-      <c r="E961" s="72"/>
-      <c r="F961" s="72"/>
-      <c r="G961" s="72"/>
-      <c r="H961" s="72"/>
-      <c r="I961" s="72"/>
-      <c r="J961" s="72"/>
-      <c r="K961" s="72"/>
-      <c r="L961" s="72"/>
-      <c r="M961" s="72"/>
-      <c r="O961" s="72"/>
-      <c r="P961" s="72"/>
-      <c r="Q961" s="72"/>
-      <c r="R961" s="72"/>
-      <c r="S961" s="72"/>
-    </row>
-    <row r="962" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A962" s="72"/>
-      <c r="B962" s="72"/>
-      <c r="C962" s="72"/>
-      <c r="D962" s="72"/>
-      <c r="E962" s="72"/>
-      <c r="F962" s="72"/>
-      <c r="G962" s="72"/>
-      <c r="H962" s="72"/>
-      <c r="I962" s="72"/>
-      <c r="J962" s="72"/>
-      <c r="K962" s="72"/>
-      <c r="L962" s="72"/>
-      <c r="M962" s="72"/>
-      <c r="O962" s="72"/>
-      <c r="P962" s="72"/>
-      <c r="Q962" s="72"/>
-      <c r="R962" s="72"/>
-      <c r="S962" s="72"/>
-    </row>
-    <row r="963" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A963" s="72"/>
-      <c r="B963" s="72"/>
-      <c r="C963" s="72"/>
-      <c r="D963" s="72"/>
-      <c r="E963" s="72"/>
-      <c r="F963" s="72"/>
-      <c r="G963" s="72"/>
-      <c r="H963" s="72"/>
-      <c r="I963" s="72"/>
-      <c r="J963" s="72"/>
-      <c r="K963" s="72"/>
-      <c r="L963" s="72"/>
-      <c r="M963" s="72"/>
-      <c r="O963" s="72"/>
-      <c r="P963" s="72"/>
-      <c r="Q963" s="72"/>
-      <c r="R963" s="72"/>
-      <c r="S963" s="72"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:F30">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+  <conditionalFormatting sqref="C4:F12">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42303,25 +41328,25 @@
           <x14:formula1>
             <xm:f>Tabela!$A$2:$A$54</xm:f>
           </x14:formula1>
-          <xm:sqref>B4:B30</xm:sqref>
+          <xm:sqref>B4:B12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{73D4FFD1-98AF-4889-A299-A52DA21564BA}">
           <x14:formula1>
             <xm:f>Tabela!$E$2:$E$29</xm:f>
           </x14:formula1>
-          <xm:sqref>S4:S30</xm:sqref>
+          <xm:sqref>S4:S12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4474925B-E8CF-49CE-90D1-0FE61A3C1612}">
           <x14:formula1>
             <xm:f>Tabela!$N$2:$N$124</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A30</xm:sqref>
+          <xm:sqref>A4:A12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{745F2A06-3BA2-4400-86DC-67500B67DDA8}">
           <x14:formula1>
             <xm:f>Tabela!$C$2:$C$10</xm:f>
           </x14:formula1>
-          <xm:sqref>R4:R30</xm:sqref>
+          <xm:sqref>R4:R12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -42769,7 +41794,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="134" t="s">
+      <c r="A11" s="126" t="s">
         <v>202</v>
       </c>
       <c r="E11" t="s">
@@ -43809,7 +42834,7 @@
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="135" t="s">
+      <c r="A54" s="127" t="s">
         <v>385</v>
       </c>
       <c r="N54" s="88" t="s">
